--- a/VerveStacks_BRA_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_BRA_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A2D81D5-2A55-4EF0-8852-5B114A59BB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5A3C7E1-1D24-4FD0-A772-4067180300BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2238,7 +2238,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB27DD29-5084-4A1E-AE3E-A083ED42AABB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E273D31-0C89-4EB5-A5A2-557B2A6CC93F}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2295,7 +2295,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B89A20F-2548-4389-8A8A-B1A0D8251F2E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0957669-B6A2-41DF-9092-C5991DADC226}">
   <dimension ref="B9:O125"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5167,7 +5167,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AD2CD94-8368-4A4D-99A5-688172F6663D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471DF2DD-055C-45FD-B0DF-CB72810BE5A2}">
   <dimension ref="B9:T225"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11535,7 +11535,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F17054C-D452-41C5-9607-9B40D791D112}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED91FED5-3735-45ED-91C0-61E9E1E26030}">
   <dimension ref="B9:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11579,7 +11579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F80376-5CC2-4574-973C-41011F93A9BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801021E5-68CC-4926-8589-49E515A0425E}">
   <dimension ref="B9:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11628,7 +11628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956ED5E4-28D8-4BBF-A3BE-85D8F019C05B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C282CF0B-E013-4C93-B7E7-AA9CB51A4548}">
   <dimension ref="B9:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11666,7 +11666,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{765DC59C-5262-4F0A-BF68-676D7284E943}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E81453F8-F871-4271-A7CC-490E08FA466F}">
   <dimension ref="B9:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11698,7 +11698,7 @@
         <v>37</v>
       </c>
       <c r="D11">
-        <v>0.42127500000000001</v>
+        <v>0.4212749999999999</v>
       </c>
       <c r="E11" t="s">
         <v>497</v>
@@ -11712,7 +11712,7 @@
         <v>37</v>
       </c>
       <c r="D12">
-        <v>0.38925833333333326</v>
+        <v>0.38925833333333332</v>
       </c>
       <c r="E12" t="s">
         <v>497</v>
@@ -11726,7 +11726,7 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>0.45576666666666671</v>
+        <v>0.45576666666666665</v>
       </c>
       <c r="E13" t="s">
         <v>497</v>
@@ -11810,7 +11810,7 @@
         <v>37</v>
       </c>
       <c r="D19">
-        <v>0.57176666666666665</v>
+        <v>0.57176666666666676</v>
       </c>
       <c r="E19" t="s">
         <v>497</v>
@@ -11880,7 +11880,7 @@
         <v>37</v>
       </c>
       <c r="D24">
-        <v>0.6014166666666666</v>
+        <v>0.60141666666666671</v>
       </c>
       <c r="E24" t="s">
         <v>497</v>
@@ -11978,7 +11978,7 @@
         <v>37</v>
       </c>
       <c r="D31">
-        <v>0.41985</v>
+        <v>0.41985000000000006</v>
       </c>
       <c r="E31" t="s">
         <v>497</v>

--- a/VerveStacks_BRA_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_BRA_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5A3C7E1-1D24-4FD0-A772-4067180300BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D57EC5C0-8811-4BDD-9C0A-3DA2F2EC69D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2238,7 +2238,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E273D31-0C89-4EB5-A5A2-557B2A6CC93F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB09D2A1-3750-43A6-9B3D-85D34B22F664}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2295,7 +2295,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0957669-B6A2-41DF-9092-C5991DADC226}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189E0670-AA76-4AB8-82F9-B2A1AB1873E1}">
   <dimension ref="B9:O125"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5167,7 +5167,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471DF2DD-055C-45FD-B0DF-CB72810BE5A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C7990D-8F31-477A-9269-32E8997F838F}">
   <dimension ref="B9:T225"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11535,7 +11535,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED91FED5-3735-45ED-91C0-61E9E1E26030}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1FBD29F-2E35-459F-944B-7509F0C43344}">
   <dimension ref="B9:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11579,7 +11579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801021E5-68CC-4926-8589-49E515A0425E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFBD78EB-5D44-4E23-9A0E-2E67C352EC3A}">
   <dimension ref="B9:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11628,7 +11628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C282CF0B-E013-4C93-B7E7-AA9CB51A4548}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F32E325-90EB-4C52-9761-C539489174AA}">
   <dimension ref="B9:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11666,7 +11666,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E81453F8-F871-4271-A7CC-490E08FA466F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADE560BE-193F-4058-A771-380EE7EC53AD}">
   <dimension ref="B9:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11698,7 +11698,7 @@
         <v>37</v>
       </c>
       <c r="D11">
-        <v>0.4212749999999999</v>
+        <v>0.42127500000000001</v>
       </c>
       <c r="E11" t="s">
         <v>497</v>
@@ -11726,7 +11726,7 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>0.45576666666666665</v>
+        <v>0.45576666666666671</v>
       </c>
       <c r="E13" t="s">
         <v>497</v>
@@ -11810,7 +11810,7 @@
         <v>37</v>
       </c>
       <c r="D19">
-        <v>0.57176666666666676</v>
+        <v>0.57176666666666665</v>
       </c>
       <c r="E19" t="s">
         <v>497</v>
@@ -11824,7 +11824,7 @@
         <v>37</v>
       </c>
       <c r="D20">
-        <v>0.53839999999999999</v>
+        <v>0.5384000000000001</v>
       </c>
       <c r="E20" t="s">
         <v>497</v>
@@ -11838,7 +11838,7 @@
         <v>37</v>
       </c>
       <c r="D21">
-        <v>0.52988333333333337</v>
+        <v>0.52988333333333326</v>
       </c>
       <c r="E21" t="s">
         <v>497</v>
@@ -11880,7 +11880,7 @@
         <v>37</v>
       </c>
       <c r="D24">
-        <v>0.60141666666666671</v>
+        <v>0.6014166666666666</v>
       </c>
       <c r="E24" t="s">
         <v>497</v>
@@ -11936,7 +11936,7 @@
         <v>37</v>
       </c>
       <c r="D28">
-        <v>0.40105833333333329</v>
+        <v>0.40105833333333335</v>
       </c>
       <c r="E28" t="s">
         <v>497</v>
@@ -11978,7 +11978,7 @@
         <v>37</v>
       </c>
       <c r="D31">
-        <v>0.41985000000000006</v>
+        <v>0.41985</v>
       </c>
       <c r="E31" t="s">
         <v>497</v>
@@ -12006,7 +12006,7 @@
         <v>37</v>
       </c>
       <c r="D33">
-        <v>0.48840833333333333</v>
+        <v>0.48840833333333328</v>
       </c>
       <c r="E33" t="s">
         <v>497</v>
